--- a/results_task_2/deepseek/2_Y_N_TI_2_oil140.xlsx
+++ b/results_task_2/deepseek/2_Y_N_TI_2_oil140.xlsx
@@ -608,7 +608,7 @@
         <v>2.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>5</v>
@@ -670,7 +670,7 @@
         <v>1.8</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J4" t="n">
         <v>5.1</v>
